--- a/tests/workbooktests/workbooks/test_swaption.xlsx
+++ b/tests/workbooktests/workbooks/test_swaption.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B6C3088-3FEB-45C4-93ED-EA2438738610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{630079B2-E0E8-4D48-B6B3-8344A5E94B8A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{1912716C-C846-4179-9E4F-7D2BB1B0432C}"/>
   </bookViews>
@@ -22,44 +22,11 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -288,7 +255,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -378,8 +345,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Prozent" xfId="1" builtinId="5"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -712,14 +679,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBB17914-90B7-4F4C-8A77-9C3F50686491}">
   <dimension ref="A1:D79"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="34.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.6640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="28.6640625" customWidth="1"/>
+    <col min="1" max="1" width="34.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -727,34 +694,34 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" cm="1">
+      <c r="B2" s="1">
         <f t="array" ref="B2">_xll.qlSettingsSetEvaluationDate(B1)</f>
         <v>46174</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="str" cm="1">
-        <f t="array" ref="B4">_xll.qlFlatForward(B2,0.03)</f>
+      <c r="B4" s="2" t="str">
+        <f>_xll.qlFlatForward(B2,0.03,"actual365fixed")</f>
         <v>欣[test_swaption.xlsx]FixedFloatSwaption!R4C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="str" cm="1">
+      <c r="B5" s="2" t="str">
         <f t="array" ref="B5">_xll.qlEuribor("6M",B4)</f>
         <v>欣[test_swaption.xlsx]FixedFloatSwaption!R5C2Euribor,A</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -762,7 +729,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -770,25 +737,25 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="1" cm="1">
+      <c r="B9" s="1">
         <f t="array" ref="B9">_xll.qlCalendarAdvance("Target",$B$2,B7,"ModifiedFollowing")</f>
         <v>46905</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="1" cm="1">
+      <c r="B10" s="1">
         <f t="array" ref="B10">_xll.qlCalendarAdvance("Target",$B$2,B8,"ModifiedFollowing")</f>
         <v>48001</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -796,81 +763,81 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2" t="str" cm="1">
+      <c r="B12" s="2" t="str">
         <f t="array" ref="B12">_xll.qlMakeSchedule(B9,B10,"1y",,"Target","ModifiedFollowing",,"Backward")</f>
         <v>欣[test_swaption.xlsx]FixedFloatSwaption!R12C2Schedule,A</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="str" cm="1">
+      <c r="B13" s="2" t="str">
         <f t="array" ref="B13">_xll.qlMakeSchedule(B9,B10,"6m",,"Target","ModifiedFollowing",,"Backward")</f>
         <v>欣[test_swaption.xlsx]FixedFloatSwaption!R13C2Schedule,A</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="str" cm="1">
+      <c r="B14" s="2" t="str">
         <f t="array" ref="B14">_xll.qlVanillaSwap("Payer",10000,B12,B11,"30/360",B13,B5,0,"Act/360")</f>
         <v>欣[test_swaption.xlsx]FixedFloatSwaption!R14C2VanillaSwap,A</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="1" cm="1">
+      <c r="B16" s="1">
         <f t="array" ref="B16:B20">_xll.qlScheduleDates(B12) - 2</f>
         <v>46903</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="B17" s="1">
         <v>46904</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="B18" s="1">
         <v>47271</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="B19" s="1">
         <v>47635</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="B20" s="4">
         <v>47999</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="2" t="str" cm="1">
+      <c r="B22" s="2" t="str">
         <f t="array" ref="B22">_xll.qlEuropeanExercise(B16)</f>
         <v>欣[test_swaption.xlsx]FixedFloatSwaption!R22C2EuropeanExercise,A</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>16</v>
       </c>
-      <c r="B23" s="2" t="str" cm="1">
+      <c r="B23" s="2" t="str">
         <f t="array" ref="B23">_xll.qlBermudanExercise(B16:B19)</f>
         <v>欣[test_swaption.xlsx]FixedFloatSwaption!R23C2BermudanExercise,A</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>17</v>
       </c>
@@ -878,7 +845,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -886,97 +853,97 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="2" t="str" cm="1">
+      <c r="B28" s="2" t="str">
         <f t="array" ref="B28">_xll.qlSwaption(B14,B22)</f>
         <v>欣[test_swaption.xlsx]FixedFloatSwaption!R28C2Swaption,A</v>
       </c>
-      <c r="C28" s="2" t="str" cm="1">
+      <c r="C28" s="2" t="str">
         <f t="array" ref="C28">_xll.qlSwaption(B14,B22,C25,C26)</f>
         <v>欣[test_swaption.xlsx]FixedFloatSwaption!R28C3Swaption,A</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>20</v>
       </c>
-      <c r="B29" s="2" t="str" cm="1">
+      <c r="B29" s="2" t="str">
         <f t="array" ref="B29">_xll.qlSwaption(B14,B23)</f>
         <v>欣[test_swaption.xlsx]FixedFloatSwaption!R29C2Swaption,A</v>
       </c>
-      <c r="C29" s="2" t="str" cm="1">
+      <c r="C29" s="2" t="str">
         <f t="array" ref="C29">_xll.qlSwaption(B14,B23,C25,C26)</f>
         <v>欣[test_swaption.xlsx]FixedFloatSwaption!R29C3Swaption,A</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>22</v>
       </c>
-      <c r="B31" s="2" t="str" cm="1">
+      <c r="B31" s="2" t="str">
         <f t="array" ref="B31">_xll.qlSwaptionSettlementType(B28)</f>
         <v>PHYSICAL</v>
       </c>
-      <c r="C31" s="2" t="str" cm="1">
+      <c r="C31" s="2" t="str">
         <f t="array" ref="C31">_xll.qlSwaptionSettlementType(C28)</f>
         <v>CASH</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>23</v>
       </c>
-      <c r="B32" s="2" t="str" cm="1">
+      <c r="B32" s="2" t="str">
         <f t="array" ref="B32">_xll.qlSwaptionSettlementMethod(B28)</f>
         <v>PHYSICALOTC</v>
       </c>
-      <c r="C32" s="2" t="str" cm="1">
+      <c r="C32" s="2" t="str">
         <f t="array" ref="C32">_xll.qlSwaptionSettlementMethod(C28)</f>
         <v>PARYIELDCURVE</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>24</v>
       </c>
-      <c r="B33" s="2" t="str" cm="1">
+      <c r="B33" s="2" t="str">
         <f t="array" ref="B33">_xll.qlSwaptionType(B28)</f>
         <v>PAYER</v>
       </c>
-      <c r="C33" s="2" t="str" cm="1">
+      <c r="C33" s="2" t="str">
         <f t="array" ref="C33">_xll.qlSwaptionType(C28)</f>
         <v>PAYER</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>32</v>
       </c>
-      <c r="B34" s="2" t="str" cm="1">
+      <c r="B34" s="2" t="str">
         <f t="array" ref="B34">_xll.qlSwaptionUnderlying(B28)</f>
         <v>欣[test_swaption.xlsx]FixedFloatSwaption!R34C2FixedVsFloatingSwap,A</v>
       </c>
-      <c r="C34" s="2" t="str" cm="1">
+      <c r="C34" s="2" t="str">
         <f t="array" ref="C34">_xll.qlSwaptionUnderlying(C28)</f>
         <v>欣[test_swaption.xlsx]FixedFloatSwaption!R34C3FixedVsFloatingSwap,A</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3">
       <c r="C35" s="2"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>26</v>
       </c>
-      <c r="B37" s="2" t="str" cm="1">
-        <f t="array" ref="B37">_xll.qlFlatForward(B2,0.025)</f>
+      <c r="B37" s="2" t="str">
+        <f>_xll.qlFlatForward(B2,0.025,"actual365fixed")</f>
         <v>欣[test_swaption.xlsx]FixedFloatSwaption!R37C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>25</v>
       </c>
@@ -984,133 +951,133 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>28</v>
       </c>
-      <c r="B39" s="2" t="str" cm="1">
+      <c r="B39" s="2" t="str">
         <f t="array" ref="B39">_xll.qlConstantSwaptionVolatility(B2,"NullCalendar","Unadjusted",B38,"act/365","Normal")</f>
         <v>欣[test_swaption.xlsx]FixedFloatSwaption!R39C2SwaptionVolatilityStructureHandle,A</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>27</v>
       </c>
-      <c r="B41" s="2" t="str" cm="1">
+      <c r="B41" s="2" t="str">
         <f t="array" ref="B41">_xll.qlBachelierSwaptionEngineFromQuote(B37,B38,"act/365")</f>
         <v>欣[test_swaption.xlsx]FixedFloatSwaption!R41C2BachelierSwaptionEngine,A</v>
       </c>
-      <c r="C41" t="str" cm="1">
+      <c r="C41" t="str">
         <f t="array" ref="C41">_xll.qlBachelierSwaptionEngineFromQuote(B37,B38,"act/365")</f>
         <v>欣[test_swaption.xlsx]FixedFloatSwaption!R41C3BachelierSwaptionEngine,A</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>29</v>
       </c>
-      <c r="B42" s="2" t="str" cm="1">
+      <c r="B42" s="2" t="str">
         <f t="array" ref="B42">_xll.qlBachelierSwaptionEngine(B37,B39)</f>
         <v>欣[test_swaption.xlsx]FixedFloatSwaption!R42C2BachelierSwaptionEngine,A</v>
       </c>
-      <c r="C42" t="str" cm="1">
+      <c r="C42" t="str">
         <f t="array" ref="C42">_xll.qlBachelierSwaptionEngine(B37,B39)</f>
         <v>欣[test_swaption.xlsx]FixedFloatSwaption!R42C3BachelierSwaptionEngine,A</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>30</v>
       </c>
-      <c r="B44" s="6" cm="1">
+      <c r="B44" s="6">
         <f t="array" ref="B44">_xll.qlInstrumentNPV(B28,_xll.qlInstrumentSetPricingEngine(B28,B41))</f>
         <v>128.29101161563773</v>
       </c>
-      <c r="C44" s="6" cm="1">
+      <c r="C44" s="6">
         <f t="array" ref="C44">_xll.qlInstrumentNPV(C28,_xll.qlInstrumentSetPricingEngine(C28,C41))</f>
         <v>127.03485296074462</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
         <v>30</v>
       </c>
-      <c r="B45" s="6" cm="1">
+      <c r="B45" s="6">
         <f t="array" ref="B45">_xll.qlInstrumentNPV(B28,_xll.qlInstrumentSetPricingEngine(B28,B42))</f>
         <v>128.29101161563773</v>
       </c>
-      <c r="C45" s="6" cm="1">
+      <c r="C45" s="6">
         <f t="array" ref="C45">_xll.qlInstrumentNPV(C28,_xll.qlInstrumentSetPricingEngine(C28,C42))</f>
         <v>127.03485296074462</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>33</v>
       </c>
-      <c r="B47" s="5" cm="1">
+      <c r="B47" s="5">
         <f t="array" ref="B47">_xll.qlSwaptionImpliedVolatility(B28,B44,B37,0.01,,,,,"Normal")</f>
         <v>8.000000000003938E-3</v>
       </c>
-      <c r="C47" s="5" cm="1">
+      <c r="C47" s="5">
         <f t="array" ref="C47">_xll.qlSwaptionImpliedVolatility(C28,C44,B37,0.01,,,,,"Normal")</f>
         <v>8.0000000000039363E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3">
       <c r="A48" t="s">
         <v>34</v>
       </c>
-      <c r="B48" s="6" cm="1">
+      <c r="B48" s="6">
         <f t="array" ref="B48">_xll.qlSwaptionVega(B28,B44)</f>
         <v>15310.148562733901</v>
       </c>
-      <c r="C48" s="6" cm="1">
+      <c r="C48" s="6">
         <f t="array" ref="C48">_xll.qlSwaptionVega(C28,C44)</f>
         <v>15160.239575482346</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3">
       <c r="A49" t="s">
         <v>35</v>
       </c>
-      <c r="B49" s="6" cm="1">
+      <c r="B49" s="6">
         <f t="array" ref="B49">_xll.qlSwaptionDelta(B28,B44)</f>
         <v>13984.983628933902</v>
       </c>
-      <c r="C49" s="6" cm="1">
+      <c r="C49" s="6">
         <f t="array" ref="C49">_xll.qlSwaptionDelta(C28,C44)</f>
         <v>13848.049965360837</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3">
       <c r="A50" t="s">
         <v>36</v>
       </c>
-      <c r="B50" s="6" cm="1">
+      <c r="B50" s="6">
         <f t="array" ref="B50">_xll.qlSwaptionAnnuity(B28,B44)</f>
         <v>27173.475726005141</v>
       </c>
-      <c r="C50" s="6" cm="1">
+      <c r="C50" s="6">
         <f t="array" ref="C50">_xll.qlSwaptionAnnuity(C28,C44)</f>
         <v>26907.407228400523</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3">
       <c r="A51" t="s">
         <v>37</v>
       </c>
-      <c r="B51" s="6" cm="1">
+      <c r="B51" s="6">
         <f t="array" ref="B51">_xll.qlSwaptionForwardPrice(B28,B44)</f>
         <v>134.85939517514475</v>
       </c>
-      <c r="C51" s="6" cm="1">
+      <c r="C51" s="6">
         <f t="array" ref="C51">_xll.qlSwaptionForwardPrice(C28,C44)</f>
         <v>133.53892233523567</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3">
       <c r="A53" t="s">
         <v>38</v>
       </c>
@@ -1118,89 +1085,89 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3">
       <c r="A54" t="s">
         <v>39</v>
       </c>
-      <c r="B54" s="7" cm="1">
+      <c r="B54" s="7">
         <f t="array" ref="B54">_xll.qlSwaptionImpliedVolatility(B28,B44,B37,0.01,,,,,"ShiftedLogNormal",B53)</f>
         <v>0.13306969341405267</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3">
       <c r="A55" t="s">
         <v>28</v>
       </c>
-      <c r="B55" s="2" t="str" cm="1">
+      <c r="B55" s="2" t="str">
         <f t="array" ref="B55">_xll.qlConstantSwaptionVolatility(B2,"NullCalendar","Unadjusted",B54,"act/365","ShiftedLogNormal",B53)</f>
         <v>欣[test_swaption.xlsx]FixedFloatSwaption!R55C2SwaptionVolatilityStructureHandle,A</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3">
       <c r="A57" t="s">
         <v>40</v>
       </c>
-      <c r="B57" s="2" t="str" cm="1">
+      <c r="B57" s="2" t="str">
         <f t="array" ref="B57">_xll.qlBlackSwaptionEngineFromQuote(B37,B54,"act/365",B53)</f>
         <v>欣[test_swaption.xlsx]FixedFloatSwaption!R57C2BlackSwaptionEngine,A</v>
       </c>
-      <c r="C57" s="2" t="str" cm="1">
+      <c r="C57" s="2" t="str">
         <f t="array" ref="C57">_xll.qlBlackSwaptionEngineFromQuote(B37,B54,"act/365",B53)</f>
         <v>欣[test_swaption.xlsx]FixedFloatSwaption!R57C3BlackSwaptionEngine,A</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3">
       <c r="A58" t="s">
         <v>41</v>
       </c>
-      <c r="B58" s="2" t="str" cm="1">
+      <c r="B58" s="2" t="str">
         <f t="array" ref="B58">_xll.qlBlackSwaptionEngine(B37,B55)</f>
         <v>欣[test_swaption.xlsx]FixedFloatSwaption!R58C2BlackSwaptionEngine,A</v>
       </c>
-      <c r="C58" s="2" t="str" cm="1">
+      <c r="C58" s="2" t="str">
         <f t="array" ref="C58">_xll.qlBlackSwaptionEngine(B37,B55)</f>
         <v>欣[test_swaption.xlsx]FixedFloatSwaption!R58C3BlackSwaptionEngine,A</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3">
       <c r="C59" s="2"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3">
       <c r="A60" t="s">
         <v>30</v>
       </c>
-      <c r="B60" s="6" cm="1">
+      <c r="B60" s="6">
         <f t="array" ref="B60">_xll.qlInstrumentNPV(B28,_xll.qlInstrumentSetPricingEngine(B28,B57))</f>
         <v>128.29101161461412</v>
       </c>
-      <c r="C60" s="6" cm="1">
+      <c r="C60" s="6">
         <f t="array" ref="C60">_xll.qlInstrumentNPV(C28,_xll.qlInstrumentSetPricingEngine(C28,C57))</f>
         <v>127.03485295973103</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3">
       <c r="A61" t="s">
         <v>30</v>
       </c>
-      <c r="B61" s="6" cm="1">
+      <c r="B61" s="6">
         <f t="array" ref="B61">_xll.qlInstrumentNPV(B28,_xll.qlInstrumentSetPricingEngine(B28,B58))</f>
         <v>128.29101161461412</v>
       </c>
-      <c r="C61" s="6" cm="1">
+      <c r="C61" s="6">
         <f t="array" ref="C61">_xll.qlInstrumentNPV(C28,_xll.qlInstrumentSetPricingEngine(C28,C58))</f>
         <v>127.03485295973103</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3">
       <c r="A64" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4">
       <c r="A66" t="s">
         <v>43</v>
       </c>
-      <c r="B66" s="2" t="str" cm="1">
+      <c r="B66" s="2" t="str">
         <f t="array" ref="B66">_xll.qlEuriborSwapIsdaFixA("1y",B4,B37)</f>
         <v>欣[test_swaption.xlsx]FixedFloatSwaption!R66C2EuriborSwapIsdaFixA,A</v>
       </c>
@@ -1208,7 +1175,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4">
       <c r="A67" t="s">
         <v>45</v>
       </c>
@@ -1219,7 +1186,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4">
       <c r="A68" t="s">
         <v>47</v>
       </c>
@@ -1230,7 +1197,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4">
       <c r="A69" t="s">
         <v>49</v>
       </c>
@@ -1241,7 +1208,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4">
       <c r="A70" t="s">
         <v>17</v>
       </c>
@@ -1252,7 +1219,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -1263,7 +1230,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4">
       <c r="A72" t="s">
         <v>53</v>
       </c>
@@ -1274,7 +1241,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4">
       <c r="A73" t="s">
         <v>55</v>
       </c>
@@ -1286,7 +1253,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4">
       <c r="A74" t="s">
         <v>57</v>
       </c>
@@ -1294,7 +1261,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4">
       <c r="A75" t="s">
         <v>59</v>
       </c>
@@ -1302,7 +1269,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4">
       <c r="A76" t="s">
         <v>61</v>
       </c>
@@ -1310,7 +1277,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4">
       <c r="A77" t="s">
         <v>63</v>
       </c>
@@ -1318,7 +1285,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4">
       <c r="A78" t="s">
         <v>65</v>
       </c>
@@ -1326,11 +1293,11 @@
         <v>66</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" ht="15">
       <c r="A79" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B79" s="9" t="str" cm="1">
+      <c r="B79" s="9" t="str">
         <f t="array" ref="B79">_xll.qlMakeSwaption(B66,B67,B68,B69,B70,B71,B72,B73,,,,,,B2)</f>
         <v>欣[test_swaption.xlsx]FixedFloatSwaption!R79C2Swaption,A</v>
       </c>
@@ -1343,9 +1310,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B30FE01-99EF-44C3-A0A1-B8C078F70958}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1">
       <c r="A1" s="8" t="s">
         <v>42</v>
       </c>
@@ -1358,9 +1325,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6530B4F0-D710-4A61-9F69-681D1476BB4F}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1">
       <c r="A1" s="8" t="s">
         <v>42</v>
       </c>

--- a/tests/workbooktests/workbooks/test_swaption.xlsx
+++ b/tests/workbooktests/workbooks/test_swaption.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{630079B2-E0E8-4D48-B6B3-8344A5E94B8A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B345FA5-FCD6-4356-B17A-3551A0489423}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{1912716C-C846-4179-9E4F-7D2BB1B0432C}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="73">
   <si>
     <t>Evaluationdate</t>
   </si>
@@ -246,6 +246,9 @@
   </si>
   <si>
     <t>qlMakeSwaption</t>
+  </si>
+  <si>
+    <t>{=qlScheduleDates(B12) - 2}</t>
   </si>
 </sst>
 </file>
@@ -315,7 +318,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -343,6 +346,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Prozent" xfId="1" builtinId="5"/>
@@ -795,29 +801,23 @@
         <v>14</v>
       </c>
       <c r="B16" s="1">
-        <f t="array" ref="B16:B20">_xll.qlScheduleDates(B12) - 2</f>
+        <f>_xll.qlScheduleDates(B12) - 2</f>
         <v>46903</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="B17" s="1">
-        <v>46904</v>
+      <c r="B17" s="11" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="B18" s="1">
-        <v>47271</v>
-      </c>
+      <c r="B18" s="1"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="B19" s="1">
-        <v>47635</v>
-      </c>
+      <c r="B19" s="1"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="B20" s="4">
-        <v>47999</v>
-      </c>
+      <c r="B20" s="4"/>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
